--- a/Javaシステム開発WBS.xlsx
+++ b/Javaシステム開発WBS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4134B9FA-8AA8-42F6-B4E2-0C850F0064F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7194A5E-119B-438D-A2C2-B822038D7C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="150">
   <si>
     <t>このワークシートでプロジェクトのスケジュール​​を作成します。
 セル B1 には、このプロジェクトのタイトルを入力します。
@@ -724,13 +724,6 @@
     <t>松村</t>
     <rPh sb="0" eb="2">
       <t>マツムラ</t>
-    </rPh>
-    <phoneticPr fontId="29"/>
-  </si>
-  <si>
-    <t>坂上</t>
-    <rPh sb="0" eb="2">
-      <t>サカガミ</t>
     </rPh>
     <phoneticPr fontId="29"/>
   </si>
@@ -1856,6 +1849,12 @@
     <xf numFmtId="14" fontId="1" fillId="10" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1867,12 +1866,6 @@
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2559,106 +2552,106 @@
       <c r="B3" s="84" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="101" t="s">
+      <c r="C3" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="102"/>
-      <c r="E3" s="100">
+      <c r="D3" s="98"/>
+      <c r="E3" s="102">
         <v>45770</v>
       </c>
-      <c r="F3" s="100"/>
+      <c r="F3" s="102"/>
     </row>
     <row r="4" spans="1:64" ht="30" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="101" t="s">
+      <c r="C4" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="102"/>
+      <c r="D4" s="98"/>
       <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="I4" s="97">
+      <c r="I4" s="99">
         <f>I5</f>
         <v>45768</v>
       </c>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="97">
+      <c r="J4" s="100"/>
+      <c r="K4" s="100"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="100"/>
+      <c r="N4" s="100"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="99">
         <f>P5</f>
         <v>45775</v>
       </c>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="98"/>
-      <c r="S4" s="98"/>
-      <c r="T4" s="98"/>
-      <c r="U4" s="98"/>
-      <c r="V4" s="99"/>
-      <c r="W4" s="97">
+      <c r="Q4" s="100"/>
+      <c r="R4" s="100"/>
+      <c r="S4" s="100"/>
+      <c r="T4" s="100"/>
+      <c r="U4" s="100"/>
+      <c r="V4" s="101"/>
+      <c r="W4" s="99">
         <f>W5</f>
         <v>45782</v>
       </c>
-      <c r="X4" s="98"/>
-      <c r="Y4" s="98"/>
-      <c r="Z4" s="98"/>
-      <c r="AA4" s="98"/>
-      <c r="AB4" s="98"/>
-      <c r="AC4" s="99"/>
-      <c r="AD4" s="97">
+      <c r="X4" s="100"/>
+      <c r="Y4" s="100"/>
+      <c r="Z4" s="100"/>
+      <c r="AA4" s="100"/>
+      <c r="AB4" s="100"/>
+      <c r="AC4" s="101"/>
+      <c r="AD4" s="99">
         <f>AD5</f>
         <v>45789</v>
       </c>
-      <c r="AE4" s="98"/>
-      <c r="AF4" s="98"/>
-      <c r="AG4" s="98"/>
-      <c r="AH4" s="98"/>
-      <c r="AI4" s="98"/>
-      <c r="AJ4" s="99"/>
-      <c r="AK4" s="97">
+      <c r="AE4" s="100"/>
+      <c r="AF4" s="100"/>
+      <c r="AG4" s="100"/>
+      <c r="AH4" s="100"/>
+      <c r="AI4" s="100"/>
+      <c r="AJ4" s="101"/>
+      <c r="AK4" s="99">
         <f>AK5</f>
         <v>45796</v>
       </c>
-      <c r="AL4" s="98"/>
-      <c r="AM4" s="98"/>
-      <c r="AN4" s="98"/>
-      <c r="AO4" s="98"/>
-      <c r="AP4" s="98"/>
-      <c r="AQ4" s="99"/>
-      <c r="AR4" s="97">
+      <c r="AL4" s="100"/>
+      <c r="AM4" s="100"/>
+      <c r="AN4" s="100"/>
+      <c r="AO4" s="100"/>
+      <c r="AP4" s="100"/>
+      <c r="AQ4" s="101"/>
+      <c r="AR4" s="99">
         <f>AR5</f>
         <v>45803</v>
       </c>
-      <c r="AS4" s="98"/>
-      <c r="AT4" s="98"/>
-      <c r="AU4" s="98"/>
-      <c r="AV4" s="98"/>
-      <c r="AW4" s="98"/>
-      <c r="AX4" s="99"/>
-      <c r="AY4" s="97">
+      <c r="AS4" s="100"/>
+      <c r="AT4" s="100"/>
+      <c r="AU4" s="100"/>
+      <c r="AV4" s="100"/>
+      <c r="AW4" s="100"/>
+      <c r="AX4" s="101"/>
+      <c r="AY4" s="99">
         <f>AY5</f>
         <v>45810</v>
       </c>
-      <c r="AZ4" s="98"/>
-      <c r="BA4" s="98"/>
-      <c r="BB4" s="98"/>
-      <c r="BC4" s="98"/>
-      <c r="BD4" s="98"/>
-      <c r="BE4" s="99"/>
-      <c r="BF4" s="97">
+      <c r="AZ4" s="100"/>
+      <c r="BA4" s="100"/>
+      <c r="BB4" s="100"/>
+      <c r="BC4" s="100"/>
+      <c r="BD4" s="100"/>
+      <c r="BE4" s="101"/>
+      <c r="BF4" s="99">
         <f>BF5</f>
         <v>45817</v>
       </c>
-      <c r="BG4" s="98"/>
-      <c r="BH4" s="98"/>
-      <c r="BI4" s="98"/>
-      <c r="BJ4" s="98"/>
-      <c r="BK4" s="98"/>
-      <c r="BL4" s="99"/>
+      <c r="BG4" s="100"/>
+      <c r="BH4" s="100"/>
+      <c r="BI4" s="100"/>
+      <c r="BJ4" s="100"/>
+      <c r="BK4" s="100"/>
+      <c r="BL4" s="101"/>
     </row>
     <row r="5" spans="1:64" ht="15" customHeight="1">
       <c r="A5" s="9" t="s">
@@ -4077,7 +4070,7 @@
         <v>144</v>
       </c>
       <c r="D19" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="94">
         <v>45770</v>
@@ -7624,7 +7617,7 @@
         <v>87</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D65" s="42">
         <v>0</v>
@@ -11307,17 +11300,17 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="11">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
   </mergeCells>
   <phoneticPr fontId="29"/>
   <conditionalFormatting sqref="D7:D112">
@@ -11494,15 +11487,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -11709,6 +11693,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11721,14 +11714,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B636D13B-D6CE-437F-B40B-151CC8DA2A1F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11747,6 +11732,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>

--- a/Javaシステム開発WBS.xlsx
+++ b/Javaシステム開発WBS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7194A5E-119B-438D-A2C2-B822038D7C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F83E87F-EB9D-4152-A4AA-8A3523E3FEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1849,12 +1849,6 @@
     <xf numFmtId="14" fontId="1" fillId="10" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1866,6 +1860,12 @@
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2552,106 +2552,106 @@
       <c r="B3" s="84" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="97" t="s">
+      <c r="C3" s="101" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="98"/>
-      <c r="E3" s="102">
+      <c r="D3" s="102"/>
+      <c r="E3" s="100">
         <v>45770</v>
       </c>
-      <c r="F3" s="102"/>
+      <c r="F3" s="100"/>
     </row>
     <row r="4" spans="1:64" ht="30" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="97" t="s">
+      <c r="C4" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="98"/>
+      <c r="D4" s="102"/>
       <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="I4" s="99">
+      <c r="I4" s="97">
         <f>I5</f>
         <v>45768</v>
       </c>
-      <c r="J4" s="100"/>
-      <c r="K4" s="100"/>
-      <c r="L4" s="100"/>
-      <c r="M4" s="100"/>
-      <c r="N4" s="100"/>
-      <c r="O4" s="101"/>
-      <c r="P4" s="99">
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="97">
         <f>P5</f>
         <v>45775</v>
       </c>
-      <c r="Q4" s="100"/>
-      <c r="R4" s="100"/>
-      <c r="S4" s="100"/>
-      <c r="T4" s="100"/>
-      <c r="U4" s="100"/>
-      <c r="V4" s="101"/>
-      <c r="W4" s="99">
+      <c r="Q4" s="98"/>
+      <c r="R4" s="98"/>
+      <c r="S4" s="98"/>
+      <c r="T4" s="98"/>
+      <c r="U4" s="98"/>
+      <c r="V4" s="99"/>
+      <c r="W4" s="97">
         <f>W5</f>
         <v>45782</v>
       </c>
-      <c r="X4" s="100"/>
-      <c r="Y4" s="100"/>
-      <c r="Z4" s="100"/>
-      <c r="AA4" s="100"/>
-      <c r="AB4" s="100"/>
-      <c r="AC4" s="101"/>
-      <c r="AD4" s="99">
+      <c r="X4" s="98"/>
+      <c r="Y4" s="98"/>
+      <c r="Z4" s="98"/>
+      <c r="AA4" s="98"/>
+      <c r="AB4" s="98"/>
+      <c r="AC4" s="99"/>
+      <c r="AD4" s="97">
         <f>AD5</f>
         <v>45789</v>
       </c>
-      <c r="AE4" s="100"/>
-      <c r="AF4" s="100"/>
-      <c r="AG4" s="100"/>
-      <c r="AH4" s="100"/>
-      <c r="AI4" s="100"/>
-      <c r="AJ4" s="101"/>
-      <c r="AK4" s="99">
+      <c r="AE4" s="98"/>
+      <c r="AF4" s="98"/>
+      <c r="AG4" s="98"/>
+      <c r="AH4" s="98"/>
+      <c r="AI4" s="98"/>
+      <c r="AJ4" s="99"/>
+      <c r="AK4" s="97">
         <f>AK5</f>
         <v>45796</v>
       </c>
-      <c r="AL4" s="100"/>
-      <c r="AM4" s="100"/>
-      <c r="AN4" s="100"/>
-      <c r="AO4" s="100"/>
-      <c r="AP4" s="100"/>
-      <c r="AQ4" s="101"/>
-      <c r="AR4" s="99">
+      <c r="AL4" s="98"/>
+      <c r="AM4" s="98"/>
+      <c r="AN4" s="98"/>
+      <c r="AO4" s="98"/>
+      <c r="AP4" s="98"/>
+      <c r="AQ4" s="99"/>
+      <c r="AR4" s="97">
         <f>AR5</f>
         <v>45803</v>
       </c>
-      <c r="AS4" s="100"/>
-      <c r="AT4" s="100"/>
-      <c r="AU4" s="100"/>
-      <c r="AV4" s="100"/>
-      <c r="AW4" s="100"/>
-      <c r="AX4" s="101"/>
-      <c r="AY4" s="99">
+      <c r="AS4" s="98"/>
+      <c r="AT4" s="98"/>
+      <c r="AU4" s="98"/>
+      <c r="AV4" s="98"/>
+      <c r="AW4" s="98"/>
+      <c r="AX4" s="99"/>
+      <c r="AY4" s="97">
         <f>AY5</f>
         <v>45810</v>
       </c>
-      <c r="AZ4" s="100"/>
-      <c r="BA4" s="100"/>
-      <c r="BB4" s="100"/>
-      <c r="BC4" s="100"/>
-      <c r="BD4" s="100"/>
-      <c r="BE4" s="101"/>
-      <c r="BF4" s="99">
+      <c r="AZ4" s="98"/>
+      <c r="BA4" s="98"/>
+      <c r="BB4" s="98"/>
+      <c r="BC4" s="98"/>
+      <c r="BD4" s="98"/>
+      <c r="BE4" s="99"/>
+      <c r="BF4" s="97">
         <f>BF5</f>
         <v>45817</v>
       </c>
-      <c r="BG4" s="100"/>
-      <c r="BH4" s="100"/>
-      <c r="BI4" s="100"/>
-      <c r="BJ4" s="100"/>
-      <c r="BK4" s="100"/>
-      <c r="BL4" s="101"/>
+      <c r="BG4" s="98"/>
+      <c r="BH4" s="98"/>
+      <c r="BI4" s="98"/>
+      <c r="BJ4" s="98"/>
+      <c r="BK4" s="98"/>
+      <c r="BL4" s="99"/>
     </row>
     <row r="5" spans="1:64" ht="15" customHeight="1">
       <c r="A5" s="9" t="s">
@@ -4228,7 +4228,7 @@
         <v>145</v>
       </c>
       <c r="D21" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="94">
         <v>45770</v>
@@ -11300,17 +11300,17 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="11">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
   </mergeCells>
   <phoneticPr fontId="29"/>
   <conditionalFormatting sqref="D7:D112">
@@ -11487,6 +11487,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -11693,15 +11702,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11714,6 +11714,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B636D13B-D6CE-437F-B40B-151CC8DA2A1F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11732,14 +11740,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>

--- a/Javaシステム開発WBS.xlsx
+++ b/Javaシステム開発WBS.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F83E87F-EB9D-4152-A4AA-8A3523E3FEE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF35918-B1D1-4DF9-903F-C7242DA0D28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1849,6 +1849,12 @@
     <xf numFmtId="14" fontId="1" fillId="10" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1860,12 +1866,6 @@
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2552,106 +2552,106 @@
       <c r="B3" s="84" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="101" t="s">
+      <c r="C3" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="102"/>
-      <c r="E3" s="100">
+      <c r="D3" s="98"/>
+      <c r="E3" s="102">
         <v>45770</v>
       </c>
-      <c r="F3" s="100"/>
+      <c r="F3" s="102"/>
     </row>
     <row r="4" spans="1:64" ht="30" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="101" t="s">
+      <c r="C4" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="102"/>
+      <c r="D4" s="98"/>
       <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="I4" s="97">
+      <c r="I4" s="99">
         <f>I5</f>
         <v>45768</v>
       </c>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="97">
+      <c r="J4" s="100"/>
+      <c r="K4" s="100"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="100"/>
+      <c r="N4" s="100"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="99">
         <f>P5</f>
         <v>45775</v>
       </c>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="98"/>
-      <c r="S4" s="98"/>
-      <c r="T4" s="98"/>
-      <c r="U4" s="98"/>
-      <c r="V4" s="99"/>
-      <c r="W4" s="97">
+      <c r="Q4" s="100"/>
+      <c r="R4" s="100"/>
+      <c r="S4" s="100"/>
+      <c r="T4" s="100"/>
+      <c r="U4" s="100"/>
+      <c r="V4" s="101"/>
+      <c r="W4" s="99">
         <f>W5</f>
         <v>45782</v>
       </c>
-      <c r="X4" s="98"/>
-      <c r="Y4" s="98"/>
-      <c r="Z4" s="98"/>
-      <c r="AA4" s="98"/>
-      <c r="AB4" s="98"/>
-      <c r="AC4" s="99"/>
-      <c r="AD4" s="97">
+      <c r="X4" s="100"/>
+      <c r="Y4" s="100"/>
+      <c r="Z4" s="100"/>
+      <c r="AA4" s="100"/>
+      <c r="AB4" s="100"/>
+      <c r="AC4" s="101"/>
+      <c r="AD4" s="99">
         <f>AD5</f>
         <v>45789</v>
       </c>
-      <c r="AE4" s="98"/>
-      <c r="AF4" s="98"/>
-      <c r="AG4" s="98"/>
-      <c r="AH4" s="98"/>
-      <c r="AI4" s="98"/>
-      <c r="AJ4" s="99"/>
-      <c r="AK4" s="97">
+      <c r="AE4" s="100"/>
+      <c r="AF4" s="100"/>
+      <c r="AG4" s="100"/>
+      <c r="AH4" s="100"/>
+      <c r="AI4" s="100"/>
+      <c r="AJ4" s="101"/>
+      <c r="AK4" s="99">
         <f>AK5</f>
         <v>45796</v>
       </c>
-      <c r="AL4" s="98"/>
-      <c r="AM4" s="98"/>
-      <c r="AN4" s="98"/>
-      <c r="AO4" s="98"/>
-      <c r="AP4" s="98"/>
-      <c r="AQ4" s="99"/>
-      <c r="AR4" s="97">
+      <c r="AL4" s="100"/>
+      <c r="AM4" s="100"/>
+      <c r="AN4" s="100"/>
+      <c r="AO4" s="100"/>
+      <c r="AP4" s="100"/>
+      <c r="AQ4" s="101"/>
+      <c r="AR4" s="99">
         <f>AR5</f>
         <v>45803</v>
       </c>
-      <c r="AS4" s="98"/>
-      <c r="AT4" s="98"/>
-      <c r="AU4" s="98"/>
-      <c r="AV4" s="98"/>
-      <c r="AW4" s="98"/>
-      <c r="AX4" s="99"/>
-      <c r="AY4" s="97">
+      <c r="AS4" s="100"/>
+      <c r="AT4" s="100"/>
+      <c r="AU4" s="100"/>
+      <c r="AV4" s="100"/>
+      <c r="AW4" s="100"/>
+      <c r="AX4" s="101"/>
+      <c r="AY4" s="99">
         <f>AY5</f>
         <v>45810</v>
       </c>
-      <c r="AZ4" s="98"/>
-      <c r="BA4" s="98"/>
-      <c r="BB4" s="98"/>
-      <c r="BC4" s="98"/>
-      <c r="BD4" s="98"/>
-      <c r="BE4" s="99"/>
-      <c r="BF4" s="97">
+      <c r="AZ4" s="100"/>
+      <c r="BA4" s="100"/>
+      <c r="BB4" s="100"/>
+      <c r="BC4" s="100"/>
+      <c r="BD4" s="100"/>
+      <c r="BE4" s="101"/>
+      <c r="BF4" s="99">
         <f>BF5</f>
         <v>45817</v>
       </c>
-      <c r="BG4" s="98"/>
-      <c r="BH4" s="98"/>
-      <c r="BI4" s="98"/>
-      <c r="BJ4" s="98"/>
-      <c r="BK4" s="98"/>
-      <c r="BL4" s="99"/>
+      <c r="BG4" s="100"/>
+      <c r="BH4" s="100"/>
+      <c r="BI4" s="100"/>
+      <c r="BJ4" s="100"/>
+      <c r="BK4" s="100"/>
+      <c r="BL4" s="101"/>
     </row>
     <row r="5" spans="1:64" ht="15" customHeight="1">
       <c r="A5" s="9" t="s">
@@ -4380,7 +4380,7 @@
         <v>145</v>
       </c>
       <c r="D23" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="94">
         <v>45771</v>
@@ -11300,17 +11300,17 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="11">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
   </mergeCells>
   <phoneticPr fontId="29"/>
   <conditionalFormatting sqref="D7:D112">
@@ -11487,15 +11487,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -11702,6 +11693,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11714,14 +11714,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B636D13B-D6CE-437F-B40B-151CC8DA2A1F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11740,6 +11732,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>

--- a/Javaシステム開発WBS.xlsx
+++ b/Javaシステム開発WBS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF35918-B1D1-4DF9-903F-C7242DA0D28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31822DB9-C9A9-44EF-B2AF-F2C9ADBFBFFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクトのスケジュール" sheetId="11" r:id="rId1"/>
@@ -1849,12 +1849,6 @@
     <xf numFmtId="14" fontId="1" fillId="10" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1866,6 +1860,12 @@
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2552,106 +2552,106 @@
       <c r="B3" s="84" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="97" t="s">
+      <c r="C3" s="101" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="98"/>
-      <c r="E3" s="102">
+      <c r="D3" s="102"/>
+      <c r="E3" s="100">
         <v>45770</v>
       </c>
-      <c r="F3" s="102"/>
+      <c r="F3" s="100"/>
     </row>
     <row r="4" spans="1:64" ht="30" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="97" t="s">
+      <c r="C4" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="98"/>
+      <c r="D4" s="102"/>
       <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="I4" s="99">
+      <c r="I4" s="97">
         <f>I5</f>
         <v>45768</v>
       </c>
-      <c r="J4" s="100"/>
-      <c r="K4" s="100"/>
-      <c r="L4" s="100"/>
-      <c r="M4" s="100"/>
-      <c r="N4" s="100"/>
-      <c r="O4" s="101"/>
-      <c r="P4" s="99">
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="97">
         <f>P5</f>
         <v>45775</v>
       </c>
-      <c r="Q4" s="100"/>
-      <c r="R4" s="100"/>
-      <c r="S4" s="100"/>
-      <c r="T4" s="100"/>
-      <c r="U4" s="100"/>
-      <c r="V4" s="101"/>
-      <c r="W4" s="99">
+      <c r="Q4" s="98"/>
+      <c r="R4" s="98"/>
+      <c r="S4" s="98"/>
+      <c r="T4" s="98"/>
+      <c r="U4" s="98"/>
+      <c r="V4" s="99"/>
+      <c r="W4" s="97">
         <f>W5</f>
         <v>45782</v>
       </c>
-      <c r="X4" s="100"/>
-      <c r="Y4" s="100"/>
-      <c r="Z4" s="100"/>
-      <c r="AA4" s="100"/>
-      <c r="AB4" s="100"/>
-      <c r="AC4" s="101"/>
-      <c r="AD4" s="99">
+      <c r="X4" s="98"/>
+      <c r="Y4" s="98"/>
+      <c r="Z4" s="98"/>
+      <c r="AA4" s="98"/>
+      <c r="AB4" s="98"/>
+      <c r="AC4" s="99"/>
+      <c r="AD4" s="97">
         <f>AD5</f>
         <v>45789</v>
       </c>
-      <c r="AE4" s="100"/>
-      <c r="AF4" s="100"/>
-      <c r="AG4" s="100"/>
-      <c r="AH4" s="100"/>
-      <c r="AI4" s="100"/>
-      <c r="AJ4" s="101"/>
-      <c r="AK4" s="99">
+      <c r="AE4" s="98"/>
+      <c r="AF4" s="98"/>
+      <c r="AG4" s="98"/>
+      <c r="AH4" s="98"/>
+      <c r="AI4" s="98"/>
+      <c r="AJ4" s="99"/>
+      <c r="AK4" s="97">
         <f>AK5</f>
         <v>45796</v>
       </c>
-      <c r="AL4" s="100"/>
-      <c r="AM4" s="100"/>
-      <c r="AN4" s="100"/>
-      <c r="AO4" s="100"/>
-      <c r="AP4" s="100"/>
-      <c r="AQ4" s="101"/>
-      <c r="AR4" s="99">
+      <c r="AL4" s="98"/>
+      <c r="AM4" s="98"/>
+      <c r="AN4" s="98"/>
+      <c r="AO4" s="98"/>
+      <c r="AP4" s="98"/>
+      <c r="AQ4" s="99"/>
+      <c r="AR4" s="97">
         <f>AR5</f>
         <v>45803</v>
       </c>
-      <c r="AS4" s="100"/>
-      <c r="AT4" s="100"/>
-      <c r="AU4" s="100"/>
-      <c r="AV4" s="100"/>
-      <c r="AW4" s="100"/>
-      <c r="AX4" s="101"/>
-      <c r="AY4" s="99">
+      <c r="AS4" s="98"/>
+      <c r="AT4" s="98"/>
+      <c r="AU4" s="98"/>
+      <c r="AV4" s="98"/>
+      <c r="AW4" s="98"/>
+      <c r="AX4" s="99"/>
+      <c r="AY4" s="97">
         <f>AY5</f>
         <v>45810</v>
       </c>
-      <c r="AZ4" s="100"/>
-      <c r="BA4" s="100"/>
-      <c r="BB4" s="100"/>
-      <c r="BC4" s="100"/>
-      <c r="BD4" s="100"/>
-      <c r="BE4" s="101"/>
-      <c r="BF4" s="99">
+      <c r="AZ4" s="98"/>
+      <c r="BA4" s="98"/>
+      <c r="BB4" s="98"/>
+      <c r="BC4" s="98"/>
+      <c r="BD4" s="98"/>
+      <c r="BE4" s="99"/>
+      <c r="BF4" s="97">
         <f>BF5</f>
         <v>45817</v>
       </c>
-      <c r="BG4" s="100"/>
-      <c r="BH4" s="100"/>
-      <c r="BI4" s="100"/>
-      <c r="BJ4" s="100"/>
-      <c r="BK4" s="100"/>
-      <c r="BL4" s="101"/>
+      <c r="BG4" s="98"/>
+      <c r="BH4" s="98"/>
+      <c r="BI4" s="98"/>
+      <c r="BJ4" s="98"/>
+      <c r="BK4" s="98"/>
+      <c r="BL4" s="99"/>
     </row>
     <row r="5" spans="1:64" ht="15" customHeight="1">
       <c r="A5" s="9" t="s">
@@ -7775,7 +7775,7 @@
         <v>149</v>
       </c>
       <c r="D67" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" s="94">
         <v>45784</v>
@@ -7851,7 +7851,7 @@
         <v>149</v>
       </c>
       <c r="D68" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="94">
         <v>45785</v>
@@ -8240,7 +8240,7 @@
         <v>149</v>
       </c>
       <c r="D73" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" s="94">
         <v>45770</v>
@@ -8319,7 +8319,7 @@
         <v>149</v>
       </c>
       <c r="D74" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" s="94">
         <v>45774</v>
@@ -11300,17 +11300,17 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="11">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
   </mergeCells>
   <phoneticPr fontId="29"/>
   <conditionalFormatting sqref="D7:D112">
@@ -11487,6 +11487,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -11693,15 +11702,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11714,6 +11714,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B636D13B-D6CE-437F-B40B-151CC8DA2A1F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11732,14 +11740,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>

--- a/Javaシステム開発WBS.xlsx
+++ b/Javaシステム開発WBS.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31822DB9-C9A9-44EF-B2AF-F2C9ADBFBFFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A28A0D9-D268-47D6-8638-255A4FF587F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2700" yWindow="950" windowWidth="15130" windowHeight="8470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクトのスケジュール" sheetId="11" r:id="rId1"/>
@@ -4304,7 +4304,7 @@
         <v>144</v>
       </c>
       <c r="D22" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="94">
         <v>45771</v>
@@ -4766,7 +4766,7 @@
         <v>146</v>
       </c>
       <c r="D28" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="95">
         <v>45770</v>
@@ -4924,7 +4924,7 @@
         <v>146</v>
       </c>
       <c r="D30" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="95">
         <v>45770</v>
@@ -5000,7 +5000,7 @@
         <v>146</v>
       </c>
       <c r="D31" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="95">
         <v>45770</v>
@@ -5076,7 +5076,7 @@
         <v>146</v>
       </c>
       <c r="D32" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="95">
         <v>45770</v>
@@ -6922,7 +6922,7 @@
         <v>147</v>
       </c>
       <c r="D56" s="39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" s="93">
         <v>45770</v>
@@ -7003,7 +7003,7 @@
         <v>147</v>
       </c>
       <c r="D57" s="39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="93">
         <v>45770</v>
@@ -7082,7 +7082,7 @@
         <v>147</v>
       </c>
       <c r="D58" s="39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" s="93">
         <v>45775</v>
@@ -7158,7 +7158,7 @@
         <v>147</v>
       </c>
       <c r="D59" s="39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="93">
         <v>45775</v>
@@ -7234,7 +7234,7 @@
         <v>148</v>
       </c>
       <c r="D60" s="39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="93">
         <v>45770</v>
@@ -7313,7 +7313,7 @@
         <v>148</v>
       </c>
       <c r="D61" s="39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" s="93">
         <v>45770</v>
@@ -7392,7 +7392,7 @@
         <v>148</v>
       </c>
       <c r="D62" s="39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" s="93">
         <v>45775</v>
@@ -7471,7 +7471,7 @@
         <v>148</v>
       </c>
       <c r="D63" s="39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" s="93">
         <v>45775</v>
@@ -7775,7 +7775,7 @@
         <v>149</v>
       </c>
       <c r="D67" s="42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" s="94">
         <v>45784</v>
@@ -7851,7 +7851,7 @@
         <v>149</v>
       </c>
       <c r="D68" s="42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" s="94">
         <v>45785</v>
@@ -8240,7 +8240,7 @@
         <v>149</v>
       </c>
       <c r="D73" s="42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73" s="94">
         <v>45770</v>
@@ -8319,7 +8319,7 @@
         <v>149</v>
       </c>
       <c r="D74" s="42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74" s="94">
         <v>45774</v>

--- a/Javaシステム開発WBS.xlsx
+++ b/Javaシステム開発WBS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A28A0D9-D268-47D6-8638-255A4FF587F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0FE54A-B73B-4585-809A-D6A33986C71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2700" yWindow="950" windowWidth="15130" windowHeight="8470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2150" yWindow="1230" windowWidth="15130" windowHeight="8470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクトのスケジュール" sheetId="11" r:id="rId1"/>
@@ -1849,6 +1849,12 @@
     <xf numFmtId="14" fontId="1" fillId="10" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1860,12 +1866,6 @@
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2552,106 +2552,106 @@
       <c r="B3" s="84" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="101" t="s">
+      <c r="C3" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="102"/>
-      <c r="E3" s="100">
+      <c r="D3" s="98"/>
+      <c r="E3" s="102">
         <v>45770</v>
       </c>
-      <c r="F3" s="100"/>
+      <c r="F3" s="102"/>
     </row>
     <row r="4" spans="1:64" ht="30" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="101" t="s">
+      <c r="C4" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="102"/>
+      <c r="D4" s="98"/>
       <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="I4" s="97">
+      <c r="I4" s="99">
         <f>I5</f>
         <v>45768</v>
       </c>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="97">
+      <c r="J4" s="100"/>
+      <c r="K4" s="100"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="100"/>
+      <c r="N4" s="100"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="99">
         <f>P5</f>
         <v>45775</v>
       </c>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="98"/>
-      <c r="S4" s="98"/>
-      <c r="T4" s="98"/>
-      <c r="U4" s="98"/>
-      <c r="V4" s="99"/>
-      <c r="W4" s="97">
+      <c r="Q4" s="100"/>
+      <c r="R4" s="100"/>
+      <c r="S4" s="100"/>
+      <c r="T4" s="100"/>
+      <c r="U4" s="100"/>
+      <c r="V4" s="101"/>
+      <c r="W4" s="99">
         <f>W5</f>
         <v>45782</v>
       </c>
-      <c r="X4" s="98"/>
-      <c r="Y4" s="98"/>
-      <c r="Z4" s="98"/>
-      <c r="AA4" s="98"/>
-      <c r="AB4" s="98"/>
-      <c r="AC4" s="99"/>
-      <c r="AD4" s="97">
+      <c r="X4" s="100"/>
+      <c r="Y4" s="100"/>
+      <c r="Z4" s="100"/>
+      <c r="AA4" s="100"/>
+      <c r="AB4" s="100"/>
+      <c r="AC4" s="101"/>
+      <c r="AD4" s="99">
         <f>AD5</f>
         <v>45789</v>
       </c>
-      <c r="AE4" s="98"/>
-      <c r="AF4" s="98"/>
-      <c r="AG4" s="98"/>
-      <c r="AH4" s="98"/>
-      <c r="AI4" s="98"/>
-      <c r="AJ4" s="99"/>
-      <c r="AK4" s="97">
+      <c r="AE4" s="100"/>
+      <c r="AF4" s="100"/>
+      <c r="AG4" s="100"/>
+      <c r="AH4" s="100"/>
+      <c r="AI4" s="100"/>
+      <c r="AJ4" s="101"/>
+      <c r="AK4" s="99">
         <f>AK5</f>
         <v>45796</v>
       </c>
-      <c r="AL4" s="98"/>
-      <c r="AM4" s="98"/>
-      <c r="AN4" s="98"/>
-      <c r="AO4" s="98"/>
-      <c r="AP4" s="98"/>
-      <c r="AQ4" s="99"/>
-      <c r="AR4" s="97">
+      <c r="AL4" s="100"/>
+      <c r="AM4" s="100"/>
+      <c r="AN4" s="100"/>
+      <c r="AO4" s="100"/>
+      <c r="AP4" s="100"/>
+      <c r="AQ4" s="101"/>
+      <c r="AR4" s="99">
         <f>AR5</f>
         <v>45803</v>
       </c>
-      <c r="AS4" s="98"/>
-      <c r="AT4" s="98"/>
-      <c r="AU4" s="98"/>
-      <c r="AV4" s="98"/>
-      <c r="AW4" s="98"/>
-      <c r="AX4" s="99"/>
-      <c r="AY4" s="97">
+      <c r="AS4" s="100"/>
+      <c r="AT4" s="100"/>
+      <c r="AU4" s="100"/>
+      <c r="AV4" s="100"/>
+      <c r="AW4" s="100"/>
+      <c r="AX4" s="101"/>
+      <c r="AY4" s="99">
         <f>AY5</f>
         <v>45810</v>
       </c>
-      <c r="AZ4" s="98"/>
-      <c r="BA4" s="98"/>
-      <c r="BB4" s="98"/>
-      <c r="BC4" s="98"/>
-      <c r="BD4" s="98"/>
-      <c r="BE4" s="99"/>
-      <c r="BF4" s="97">
+      <c r="AZ4" s="100"/>
+      <c r="BA4" s="100"/>
+      <c r="BB4" s="100"/>
+      <c r="BC4" s="100"/>
+      <c r="BD4" s="100"/>
+      <c r="BE4" s="101"/>
+      <c r="BF4" s="99">
         <f>BF5</f>
         <v>45817</v>
       </c>
-      <c r="BG4" s="98"/>
-      <c r="BH4" s="98"/>
-      <c r="BI4" s="98"/>
-      <c r="BJ4" s="98"/>
-      <c r="BK4" s="98"/>
-      <c r="BL4" s="99"/>
+      <c r="BG4" s="100"/>
+      <c r="BH4" s="100"/>
+      <c r="BI4" s="100"/>
+      <c r="BJ4" s="100"/>
+      <c r="BK4" s="100"/>
+      <c r="BL4" s="101"/>
     </row>
     <row r="5" spans="1:64" ht="15" customHeight="1">
       <c r="A5" s="9" t="s">
@@ -8395,7 +8395,7 @@
         <v>145</v>
       </c>
       <c r="D75" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" s="94">
         <v>45774</v>
@@ -8471,7 +8471,7 @@
         <v>145</v>
       </c>
       <c r="D76" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" s="94">
         <v>45785</v>
@@ -11300,17 +11300,17 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="11">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
   </mergeCells>
   <phoneticPr fontId="29"/>
   <conditionalFormatting sqref="D7:D112">
@@ -11487,15 +11487,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -11702,6 +11693,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11714,14 +11714,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B636D13B-D6CE-437F-B40B-151CC8DA2A1F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11740,6 +11732,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>

--- a/Javaシステム開発WBS.xlsx
+++ b/Javaシステム開発WBS.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0FE54A-B73B-4585-809A-D6A33986C71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E0C283-38BA-4EFA-AE83-A31CE2661537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2150" yWindow="1230" windowWidth="15130" windowHeight="8470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="15130" windowHeight="8470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクトのスケジュール" sheetId="11" r:id="rId1"/>
@@ -1849,12 +1849,6 @@
     <xf numFmtId="14" fontId="1" fillId="10" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1866,6 +1860,12 @@
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2552,106 +2552,106 @@
       <c r="B3" s="84" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="97" t="s">
+      <c r="C3" s="101" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="98"/>
-      <c r="E3" s="102">
+      <c r="D3" s="102"/>
+      <c r="E3" s="100">
         <v>45770</v>
       </c>
-      <c r="F3" s="102"/>
+      <c r="F3" s="100"/>
     </row>
     <row r="4" spans="1:64" ht="30" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="97" t="s">
+      <c r="C4" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="98"/>
+      <c r="D4" s="102"/>
       <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="I4" s="99">
+      <c r="I4" s="97">
         <f>I5</f>
         <v>45768</v>
       </c>
-      <c r="J4" s="100"/>
-      <c r="K4" s="100"/>
-      <c r="L4" s="100"/>
-      <c r="M4" s="100"/>
-      <c r="N4" s="100"/>
-      <c r="O4" s="101"/>
-      <c r="P4" s="99">
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="97">
         <f>P5</f>
         <v>45775</v>
       </c>
-      <c r="Q4" s="100"/>
-      <c r="R4" s="100"/>
-      <c r="S4" s="100"/>
-      <c r="T4" s="100"/>
-      <c r="U4" s="100"/>
-      <c r="V4" s="101"/>
-      <c r="W4" s="99">
+      <c r="Q4" s="98"/>
+      <c r="R4" s="98"/>
+      <c r="S4" s="98"/>
+      <c r="T4" s="98"/>
+      <c r="U4" s="98"/>
+      <c r="V4" s="99"/>
+      <c r="W4" s="97">
         <f>W5</f>
         <v>45782</v>
       </c>
-      <c r="X4" s="100"/>
-      <c r="Y4" s="100"/>
-      <c r="Z4" s="100"/>
-      <c r="AA4" s="100"/>
-      <c r="AB4" s="100"/>
-      <c r="AC4" s="101"/>
-      <c r="AD4" s="99">
+      <c r="X4" s="98"/>
+      <c r="Y4" s="98"/>
+      <c r="Z4" s="98"/>
+      <c r="AA4" s="98"/>
+      <c r="AB4" s="98"/>
+      <c r="AC4" s="99"/>
+      <c r="AD4" s="97">
         <f>AD5</f>
         <v>45789</v>
       </c>
-      <c r="AE4" s="100"/>
-      <c r="AF4" s="100"/>
-      <c r="AG4" s="100"/>
-      <c r="AH4" s="100"/>
-      <c r="AI4" s="100"/>
-      <c r="AJ4" s="101"/>
-      <c r="AK4" s="99">
+      <c r="AE4" s="98"/>
+      <c r="AF4" s="98"/>
+      <c r="AG4" s="98"/>
+      <c r="AH4" s="98"/>
+      <c r="AI4" s="98"/>
+      <c r="AJ4" s="99"/>
+      <c r="AK4" s="97">
         <f>AK5</f>
         <v>45796</v>
       </c>
-      <c r="AL4" s="100"/>
-      <c r="AM4" s="100"/>
-      <c r="AN4" s="100"/>
-      <c r="AO4" s="100"/>
-      <c r="AP4" s="100"/>
-      <c r="AQ4" s="101"/>
-      <c r="AR4" s="99">
+      <c r="AL4" s="98"/>
+      <c r="AM4" s="98"/>
+      <c r="AN4" s="98"/>
+      <c r="AO4" s="98"/>
+      <c r="AP4" s="98"/>
+      <c r="AQ4" s="99"/>
+      <c r="AR4" s="97">
         <f>AR5</f>
         <v>45803</v>
       </c>
-      <c r="AS4" s="100"/>
-      <c r="AT4" s="100"/>
-      <c r="AU4" s="100"/>
-      <c r="AV4" s="100"/>
-      <c r="AW4" s="100"/>
-      <c r="AX4" s="101"/>
-      <c r="AY4" s="99">
+      <c r="AS4" s="98"/>
+      <c r="AT4" s="98"/>
+      <c r="AU4" s="98"/>
+      <c r="AV4" s="98"/>
+      <c r="AW4" s="98"/>
+      <c r="AX4" s="99"/>
+      <c r="AY4" s="97">
         <f>AY5</f>
         <v>45810</v>
       </c>
-      <c r="AZ4" s="100"/>
-      <c r="BA4" s="100"/>
-      <c r="BB4" s="100"/>
-      <c r="BC4" s="100"/>
-      <c r="BD4" s="100"/>
-      <c r="BE4" s="101"/>
-      <c r="BF4" s="99">
+      <c r="AZ4" s="98"/>
+      <c r="BA4" s="98"/>
+      <c r="BB4" s="98"/>
+      <c r="BC4" s="98"/>
+      <c r="BD4" s="98"/>
+      <c r="BE4" s="99"/>
+      <c r="BF4" s="97">
         <f>BF5</f>
         <v>45817</v>
       </c>
-      <c r="BG4" s="100"/>
-      <c r="BH4" s="100"/>
-      <c r="BI4" s="100"/>
-      <c r="BJ4" s="100"/>
-      <c r="BK4" s="100"/>
-      <c r="BL4" s="101"/>
+      <c r="BG4" s="98"/>
+      <c r="BH4" s="98"/>
+      <c r="BI4" s="98"/>
+      <c r="BJ4" s="98"/>
+      <c r="BK4" s="98"/>
+      <c r="BL4" s="99"/>
     </row>
     <row r="5" spans="1:64" ht="15" customHeight="1">
       <c r="A5" s="9" t="s">
@@ -7620,7 +7620,7 @@
         <v>144</v>
       </c>
       <c r="D65" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" s="94">
         <v>45774</v>
@@ -7699,7 +7699,7 @@
         <v>144</v>
       </c>
       <c r="D66" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" s="94">
         <v>45784</v>
@@ -7775,7 +7775,7 @@
         <v>149</v>
       </c>
       <c r="D67" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" s="94">
         <v>45784</v>
@@ -7851,7 +7851,7 @@
         <v>149</v>
       </c>
       <c r="D68" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="94">
         <v>45785</v>
@@ -7927,7 +7927,7 @@
         <v>146</v>
       </c>
       <c r="D69" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" s="94">
         <v>45771</v>
@@ -8003,7 +8003,7 @@
         <v>146</v>
       </c>
       <c r="D70" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" s="94">
         <v>45775</v>
@@ -8082,7 +8082,7 @@
         <v>146</v>
       </c>
       <c r="D71" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" s="94">
         <v>45784</v>
@@ -8161,7 +8161,7 @@
         <v>146</v>
       </c>
       <c r="D72" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" s="94">
         <v>45785</v>
@@ -8240,7 +8240,7 @@
         <v>149</v>
       </c>
       <c r="D73" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" s="94">
         <v>45770</v>
@@ -8319,7 +8319,7 @@
         <v>149</v>
       </c>
       <c r="D74" s="42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74" s="94">
         <v>45774</v>
@@ -11300,17 +11300,17 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="11">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
   </mergeCells>
   <phoneticPr fontId="29"/>
   <conditionalFormatting sqref="D7:D112">
@@ -11487,6 +11487,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -11693,15 +11702,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11714,6 +11714,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B636D13B-D6CE-437F-B40B-151CC8DA2A1F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11732,14 +11740,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>

--- a/Javaシステム開発WBS.xlsx
+++ b/Javaシステム開発WBS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E0C283-38BA-4EFA-AE83-A31CE2661537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9FE0AB-10DE-426F-A439-A56123A04428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="15130" windowHeight="8470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3160" yWindow="870" windowWidth="15130" windowHeight="8470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクトのスケジュール" sheetId="11" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="152">
   <si>
     <t>このワークシートでプロジェクトのスケジュール​​を作成します。
 セル B1 には、このプロジェクトのタイトルを入力します。
@@ -725,6 +725,14 @@
     <rPh sb="0" eb="2">
       <t>マツムラ</t>
     </rPh>
+    <phoneticPr fontId="29"/>
+  </si>
+  <si>
+    <t>増田</t>
+    <phoneticPr fontId="29"/>
+  </si>
+  <si>
+    <t>福岡</t>
     <phoneticPr fontId="29"/>
   </si>
 </sst>
@@ -1849,6 +1857,12 @@
     <xf numFmtId="14" fontId="1" fillId="10" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1860,12 +1874,6 @@
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2552,106 +2560,106 @@
       <c r="B3" s="84" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="101" t="s">
+      <c r="C3" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="102"/>
-      <c r="E3" s="100">
+      <c r="D3" s="98"/>
+      <c r="E3" s="102">
         <v>45770</v>
       </c>
-      <c r="F3" s="100"/>
+      <c r="F3" s="102"/>
     </row>
     <row r="4" spans="1:64" ht="30" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="101" t="s">
+      <c r="C4" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="102"/>
+      <c r="D4" s="98"/>
       <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="I4" s="97">
+      <c r="I4" s="99">
         <f>I5</f>
         <v>45768</v>
       </c>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="97">
+      <c r="J4" s="100"/>
+      <c r="K4" s="100"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="100"/>
+      <c r="N4" s="100"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="99">
         <f>P5</f>
         <v>45775</v>
       </c>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="98"/>
-      <c r="S4" s="98"/>
-      <c r="T4" s="98"/>
-      <c r="U4" s="98"/>
-      <c r="V4" s="99"/>
-      <c r="W4" s="97">
+      <c r="Q4" s="100"/>
+      <c r="R4" s="100"/>
+      <c r="S4" s="100"/>
+      <c r="T4" s="100"/>
+      <c r="U4" s="100"/>
+      <c r="V4" s="101"/>
+      <c r="W4" s="99">
         <f>W5</f>
         <v>45782</v>
       </c>
-      <c r="X4" s="98"/>
-      <c r="Y4" s="98"/>
-      <c r="Z4" s="98"/>
-      <c r="AA4" s="98"/>
-      <c r="AB4" s="98"/>
-      <c r="AC4" s="99"/>
-      <c r="AD4" s="97">
+      <c r="X4" s="100"/>
+      <c r="Y4" s="100"/>
+      <c r="Z4" s="100"/>
+      <c r="AA4" s="100"/>
+      <c r="AB4" s="100"/>
+      <c r="AC4" s="101"/>
+      <c r="AD4" s="99">
         <f>AD5</f>
         <v>45789</v>
       </c>
-      <c r="AE4" s="98"/>
-      <c r="AF4" s="98"/>
-      <c r="AG4" s="98"/>
-      <c r="AH4" s="98"/>
-      <c r="AI4" s="98"/>
-      <c r="AJ4" s="99"/>
-      <c r="AK4" s="97">
+      <c r="AE4" s="100"/>
+      <c r="AF4" s="100"/>
+      <c r="AG4" s="100"/>
+      <c r="AH4" s="100"/>
+      <c r="AI4" s="100"/>
+      <c r="AJ4" s="101"/>
+      <c r="AK4" s="99">
         <f>AK5</f>
         <v>45796</v>
       </c>
-      <c r="AL4" s="98"/>
-      <c r="AM4" s="98"/>
-      <c r="AN4" s="98"/>
-      <c r="AO4" s="98"/>
-      <c r="AP4" s="98"/>
-      <c r="AQ4" s="99"/>
-      <c r="AR4" s="97">
+      <c r="AL4" s="100"/>
+      <c r="AM4" s="100"/>
+      <c r="AN4" s="100"/>
+      <c r="AO4" s="100"/>
+      <c r="AP4" s="100"/>
+      <c r="AQ4" s="101"/>
+      <c r="AR4" s="99">
         <f>AR5</f>
         <v>45803</v>
       </c>
-      <c r="AS4" s="98"/>
-      <c r="AT4" s="98"/>
-      <c r="AU4" s="98"/>
-      <c r="AV4" s="98"/>
-      <c r="AW4" s="98"/>
-      <c r="AX4" s="99"/>
-      <c r="AY4" s="97">
+      <c r="AS4" s="100"/>
+      <c r="AT4" s="100"/>
+      <c r="AU4" s="100"/>
+      <c r="AV4" s="100"/>
+      <c r="AW4" s="100"/>
+      <c r="AX4" s="101"/>
+      <c r="AY4" s="99">
         <f>AY5</f>
         <v>45810</v>
       </c>
-      <c r="AZ4" s="98"/>
-      <c r="BA4" s="98"/>
-      <c r="BB4" s="98"/>
-      <c r="BC4" s="98"/>
-      <c r="BD4" s="98"/>
-      <c r="BE4" s="99"/>
-      <c r="BF4" s="97">
+      <c r="AZ4" s="100"/>
+      <c r="BA4" s="100"/>
+      <c r="BB4" s="100"/>
+      <c r="BC4" s="100"/>
+      <c r="BD4" s="100"/>
+      <c r="BE4" s="101"/>
+      <c r="BF4" s="99">
         <f>BF5</f>
         <v>45817</v>
       </c>
-      <c r="BG4" s="98"/>
-      <c r="BH4" s="98"/>
-      <c r="BI4" s="98"/>
-      <c r="BJ4" s="98"/>
-      <c r="BK4" s="98"/>
-      <c r="BL4" s="99"/>
+      <c r="BG4" s="100"/>
+      <c r="BH4" s="100"/>
+      <c r="BI4" s="100"/>
+      <c r="BJ4" s="100"/>
+      <c r="BK4" s="100"/>
+      <c r="BL4" s="101"/>
     </row>
     <row r="5" spans="1:64" ht="15" customHeight="1">
       <c r="A5" s="9" t="s">
@@ -8617,7 +8625,7 @@
         <v>100</v>
       </c>
       <c r="C78" s="17" t="s">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="D78" s="45">
         <v>0</v>
@@ -8696,7 +8704,7 @@
         <v>101</v>
       </c>
       <c r="C79" s="17" t="s">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="D79" s="45">
         <v>0</v>
@@ -8772,7 +8780,7 @@
         <v>102</v>
       </c>
       <c r="C80" s="17" t="s">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="D80" s="45">
         <v>0</v>
@@ -8848,7 +8856,7 @@
         <v>103</v>
       </c>
       <c r="C81" s="17" t="s">
-        <v>47</v>
+        <v>146</v>
       </c>
       <c r="D81" s="45">
         <v>0</v>
@@ -8924,7 +8932,7 @@
         <v>104</v>
       </c>
       <c r="C82" s="17" t="s">
-        <v>47</v>
+        <v>146</v>
       </c>
       <c r="D82" s="45">
         <v>0</v>
@@ -9000,7 +9008,7 @@
         <v>105</v>
       </c>
       <c r="C83" s="17" t="s">
-        <v>47</v>
+        <v>146</v>
       </c>
       <c r="D83" s="45">
         <v>0</v>
@@ -9076,7 +9084,7 @@
         <v>106</v>
       </c>
       <c r="C84" s="17" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="D84" s="45">
         <v>0</v>
@@ -9152,7 +9160,7 @@
         <v>107</v>
       </c>
       <c r="C85" s="17" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="D85" s="45">
         <v>0</v>
@@ -9228,7 +9236,7 @@
         <v>108</v>
       </c>
       <c r="C86" s="17" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="D86" s="45">
         <v>0</v>
@@ -9304,7 +9312,7 @@
         <v>109</v>
       </c>
       <c r="C87" s="17" t="s">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="D87" s="45">
         <v>0</v>
@@ -9380,7 +9388,7 @@
         <v>110</v>
       </c>
       <c r="C88" s="17" t="s">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="D88" s="45">
         <v>0</v>
@@ -9456,7 +9464,7 @@
         <v>111</v>
       </c>
       <c r="C89" s="17" t="s">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="D89" s="45">
         <v>0</v>
@@ -9535,7 +9543,7 @@
         <v>112</v>
       </c>
       <c r="C90" s="17" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="D90" s="45">
         <v>0</v>
@@ -9614,7 +9622,7 @@
         <v>113</v>
       </c>
       <c r="C91" s="17" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="D91" s="45">
         <v>0</v>
@@ -9693,7 +9701,7 @@
         <v>114</v>
       </c>
       <c r="C92" s="17" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="D92" s="45">
         <v>0</v>
@@ -9772,7 +9780,7 @@
         <v>115</v>
       </c>
       <c r="C93" s="17" t="s">
-        <v>82</v>
+        <v>145</v>
       </c>
       <c r="D93" s="45">
         <v>0</v>
@@ -9848,7 +9856,7 @@
         <v>116</v>
       </c>
       <c r="C94" s="17" t="s">
-        <v>35</v>
+        <v>145</v>
       </c>
       <c r="D94" s="45">
         <v>0</v>
@@ -9924,7 +9932,7 @@
         <v>117</v>
       </c>
       <c r="C95" s="17" t="s">
-        <v>38</v>
+        <v>145</v>
       </c>
       <c r="D95" s="45">
         <v>0</v>
@@ -11300,17 +11308,17 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="11">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
   </mergeCells>
   <phoneticPr fontId="29"/>
   <conditionalFormatting sqref="D7:D112">
@@ -11487,12 +11495,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11703,20 +11713,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11741,12 +11752,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Javaシステム開発WBS.xlsx
+++ b/Javaシステム開発WBS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9FE0AB-10DE-426F-A439-A56123A04428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48BB8CBE-BC27-4543-A48B-766A657B87DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3160" yWindow="870" windowWidth="15130" windowHeight="8470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3170" yWindow="800" windowWidth="15130" windowHeight="8470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクトのスケジュール" sheetId="11" r:id="rId1"/>
@@ -1857,12 +1857,6 @@
     <xf numFmtId="14" fontId="1" fillId="10" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1874,6 +1868,12 @@
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2560,106 +2560,106 @@
       <c r="B3" s="84" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="97" t="s">
+      <c r="C3" s="101" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="98"/>
-      <c r="E3" s="102">
+      <c r="D3" s="102"/>
+      <c r="E3" s="100">
         <v>45770</v>
       </c>
-      <c r="F3" s="102"/>
+      <c r="F3" s="100"/>
     </row>
     <row r="4" spans="1:64" ht="30" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="97" t="s">
+      <c r="C4" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="98"/>
+      <c r="D4" s="102"/>
       <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="I4" s="99">
+      <c r="I4" s="97">
         <f>I5</f>
         <v>45768</v>
       </c>
-      <c r="J4" s="100"/>
-      <c r="K4" s="100"/>
-      <c r="L4" s="100"/>
-      <c r="M4" s="100"/>
-      <c r="N4" s="100"/>
-      <c r="O4" s="101"/>
-      <c r="P4" s="99">
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="97">
         <f>P5</f>
         <v>45775</v>
       </c>
-      <c r="Q4" s="100"/>
-      <c r="R4" s="100"/>
-      <c r="S4" s="100"/>
-      <c r="T4" s="100"/>
-      <c r="U4" s="100"/>
-      <c r="V4" s="101"/>
-      <c r="W4" s="99">
+      <c r="Q4" s="98"/>
+      <c r="R4" s="98"/>
+      <c r="S4" s="98"/>
+      <c r="T4" s="98"/>
+      <c r="U4" s="98"/>
+      <c r="V4" s="99"/>
+      <c r="W4" s="97">
         <f>W5</f>
         <v>45782</v>
       </c>
-      <c r="X4" s="100"/>
-      <c r="Y4" s="100"/>
-      <c r="Z4" s="100"/>
-      <c r="AA4" s="100"/>
-      <c r="AB4" s="100"/>
-      <c r="AC4" s="101"/>
-      <c r="AD4" s="99">
+      <c r="X4" s="98"/>
+      <c r="Y4" s="98"/>
+      <c r="Z4" s="98"/>
+      <c r="AA4" s="98"/>
+      <c r="AB4" s="98"/>
+      <c r="AC4" s="99"/>
+      <c r="AD4" s="97">
         <f>AD5</f>
         <v>45789</v>
       </c>
-      <c r="AE4" s="100"/>
-      <c r="AF4" s="100"/>
-      <c r="AG4" s="100"/>
-      <c r="AH4" s="100"/>
-      <c r="AI4" s="100"/>
-      <c r="AJ4" s="101"/>
-      <c r="AK4" s="99">
+      <c r="AE4" s="98"/>
+      <c r="AF4" s="98"/>
+      <c r="AG4" s="98"/>
+      <c r="AH4" s="98"/>
+      <c r="AI4" s="98"/>
+      <c r="AJ4" s="99"/>
+      <c r="AK4" s="97">
         <f>AK5</f>
         <v>45796</v>
       </c>
-      <c r="AL4" s="100"/>
-      <c r="AM4" s="100"/>
-      <c r="AN4" s="100"/>
-      <c r="AO4" s="100"/>
-      <c r="AP4" s="100"/>
-      <c r="AQ4" s="101"/>
-      <c r="AR4" s="99">
+      <c r="AL4" s="98"/>
+      <c r="AM4" s="98"/>
+      <c r="AN4" s="98"/>
+      <c r="AO4" s="98"/>
+      <c r="AP4" s="98"/>
+      <c r="AQ4" s="99"/>
+      <c r="AR4" s="97">
         <f>AR5</f>
         <v>45803</v>
       </c>
-      <c r="AS4" s="100"/>
-      <c r="AT4" s="100"/>
-      <c r="AU4" s="100"/>
-      <c r="AV4" s="100"/>
-      <c r="AW4" s="100"/>
-      <c r="AX4" s="101"/>
-      <c r="AY4" s="99">
+      <c r="AS4" s="98"/>
+      <c r="AT4" s="98"/>
+      <c r="AU4" s="98"/>
+      <c r="AV4" s="98"/>
+      <c r="AW4" s="98"/>
+      <c r="AX4" s="99"/>
+      <c r="AY4" s="97">
         <f>AY5</f>
         <v>45810</v>
       </c>
-      <c r="AZ4" s="100"/>
-      <c r="BA4" s="100"/>
-      <c r="BB4" s="100"/>
-      <c r="BC4" s="100"/>
-      <c r="BD4" s="100"/>
-      <c r="BE4" s="101"/>
-      <c r="BF4" s="99">
+      <c r="AZ4" s="98"/>
+      <c r="BA4" s="98"/>
+      <c r="BB4" s="98"/>
+      <c r="BC4" s="98"/>
+      <c r="BD4" s="98"/>
+      <c r="BE4" s="99"/>
+      <c r="BF4" s="97">
         <f>BF5</f>
         <v>45817</v>
       </c>
-      <c r="BG4" s="100"/>
-      <c r="BH4" s="100"/>
-      <c r="BI4" s="100"/>
-      <c r="BJ4" s="100"/>
-      <c r="BK4" s="100"/>
-      <c r="BL4" s="101"/>
+      <c r="BG4" s="98"/>
+      <c r="BH4" s="98"/>
+      <c r="BI4" s="98"/>
+      <c r="BJ4" s="98"/>
+      <c r="BK4" s="98"/>
+      <c r="BL4" s="99"/>
     </row>
     <row r="5" spans="1:64" ht="15" customHeight="1">
       <c r="A5" s="9" t="s">
@@ -8627,8 +8627,8 @@
       <c r="C78" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="D78" s="45">
-        <v>0</v>
+      <c r="D78" s="42">
+        <v>1</v>
       </c>
       <c r="E78" s="95">
         <v>45784</v>
@@ -8706,8 +8706,8 @@
       <c r="C79" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="D79" s="45">
-        <v>0</v>
+      <c r="D79" s="42">
+        <v>1</v>
       </c>
       <c r="E79" s="95">
         <v>45784</v>
@@ -8782,8 +8782,8 @@
       <c r="C80" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="D80" s="45">
-        <v>0</v>
+      <c r="D80" s="42">
+        <v>1</v>
       </c>
       <c r="E80" s="95">
         <v>45784</v>
@@ -10008,7 +10008,7 @@
         <v>118</v>
       </c>
       <c r="C96" s="17" t="s">
-        <v>82</v>
+        <v>145</v>
       </c>
       <c r="D96" s="45">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>119</v>
       </c>
       <c r="C97" s="17" t="s">
-        <v>35</v>
+        <v>145</v>
       </c>
       <c r="D97" s="45">
         <v>0</v>
@@ -10160,7 +10160,7 @@
         <v>120</v>
       </c>
       <c r="C98" s="17" t="s">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="D98" s="45">
         <v>0</v>
@@ -11308,17 +11308,17 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="11">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
   </mergeCells>
   <phoneticPr fontId="29"/>
   <conditionalFormatting sqref="D7:D112">
@@ -11495,17 +11495,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -11712,6 +11701,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -11722,17 +11722,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B636D13B-D6CE-437F-B40B-151CC8DA2A1F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11751,6 +11740,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
   <ds:schemaRefs>

--- a/Javaシステム開発WBS.xlsx
+++ b/Javaシステム開発WBS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48BB8CBE-BC27-4543-A48B-766A657B87DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7A7D55-43BB-432F-B834-6B4F06247617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3170" yWindow="800" windowWidth="15130" windowHeight="8470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクトのスケジュール" sheetId="11" r:id="rId1"/>
@@ -1857,6 +1857,12 @@
     <xf numFmtId="14" fontId="1" fillId="10" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1868,12 +1874,6 @@
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2560,106 +2560,106 @@
       <c r="B3" s="84" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="101" t="s">
+      <c r="C3" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="102"/>
-      <c r="E3" s="100">
+      <c r="D3" s="98"/>
+      <c r="E3" s="102">
         <v>45770</v>
       </c>
-      <c r="F3" s="100"/>
+      <c r="F3" s="102"/>
     </row>
     <row r="4" spans="1:64" ht="30" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="101" t="s">
+      <c r="C4" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="102"/>
+      <c r="D4" s="98"/>
       <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="I4" s="97">
+      <c r="I4" s="99">
         <f>I5</f>
         <v>45768</v>
       </c>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="97">
+      <c r="J4" s="100"/>
+      <c r="K4" s="100"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="100"/>
+      <c r="N4" s="100"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="99">
         <f>P5</f>
         <v>45775</v>
       </c>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="98"/>
-      <c r="S4" s="98"/>
-      <c r="T4" s="98"/>
-      <c r="U4" s="98"/>
-      <c r="V4" s="99"/>
-      <c r="W4" s="97">
+      <c r="Q4" s="100"/>
+      <c r="R4" s="100"/>
+      <c r="S4" s="100"/>
+      <c r="T4" s="100"/>
+      <c r="U4" s="100"/>
+      <c r="V4" s="101"/>
+      <c r="W4" s="99">
         <f>W5</f>
         <v>45782</v>
       </c>
-      <c r="X4" s="98"/>
-      <c r="Y4" s="98"/>
-      <c r="Z4" s="98"/>
-      <c r="AA4" s="98"/>
-      <c r="AB4" s="98"/>
-      <c r="AC4" s="99"/>
-      <c r="AD4" s="97">
+      <c r="X4" s="100"/>
+      <c r="Y4" s="100"/>
+      <c r="Z4" s="100"/>
+      <c r="AA4" s="100"/>
+      <c r="AB4" s="100"/>
+      <c r="AC4" s="101"/>
+      <c r="AD4" s="99">
         <f>AD5</f>
         <v>45789</v>
       </c>
-      <c r="AE4" s="98"/>
-      <c r="AF4" s="98"/>
-      <c r="AG4" s="98"/>
-      <c r="AH4" s="98"/>
-      <c r="AI4" s="98"/>
-      <c r="AJ4" s="99"/>
-      <c r="AK4" s="97">
+      <c r="AE4" s="100"/>
+      <c r="AF4" s="100"/>
+      <c r="AG4" s="100"/>
+      <c r="AH4" s="100"/>
+      <c r="AI4" s="100"/>
+      <c r="AJ4" s="101"/>
+      <c r="AK4" s="99">
         <f>AK5</f>
         <v>45796</v>
       </c>
-      <c r="AL4" s="98"/>
-      <c r="AM4" s="98"/>
-      <c r="AN4" s="98"/>
-      <c r="AO4" s="98"/>
-      <c r="AP4" s="98"/>
-      <c r="AQ4" s="99"/>
-      <c r="AR4" s="97">
+      <c r="AL4" s="100"/>
+      <c r="AM4" s="100"/>
+      <c r="AN4" s="100"/>
+      <c r="AO4" s="100"/>
+      <c r="AP4" s="100"/>
+      <c r="AQ4" s="101"/>
+      <c r="AR4" s="99">
         <f>AR5</f>
         <v>45803</v>
       </c>
-      <c r="AS4" s="98"/>
-      <c r="AT4" s="98"/>
-      <c r="AU4" s="98"/>
-      <c r="AV4" s="98"/>
-      <c r="AW4" s="98"/>
-      <c r="AX4" s="99"/>
-      <c r="AY4" s="97">
+      <c r="AS4" s="100"/>
+      <c r="AT4" s="100"/>
+      <c r="AU4" s="100"/>
+      <c r="AV4" s="100"/>
+      <c r="AW4" s="100"/>
+      <c r="AX4" s="101"/>
+      <c r="AY4" s="99">
         <f>AY5</f>
         <v>45810</v>
       </c>
-      <c r="AZ4" s="98"/>
-      <c r="BA4" s="98"/>
-      <c r="BB4" s="98"/>
-      <c r="BC4" s="98"/>
-      <c r="BD4" s="98"/>
-      <c r="BE4" s="99"/>
-      <c r="BF4" s="97">
+      <c r="AZ4" s="100"/>
+      <c r="BA4" s="100"/>
+      <c r="BB4" s="100"/>
+      <c r="BC4" s="100"/>
+      <c r="BD4" s="100"/>
+      <c r="BE4" s="101"/>
+      <c r="BF4" s="99">
         <f>BF5</f>
         <v>45817</v>
       </c>
-      <c r="BG4" s="98"/>
-      <c r="BH4" s="98"/>
-      <c r="BI4" s="98"/>
-      <c r="BJ4" s="98"/>
-      <c r="BK4" s="98"/>
-      <c r="BL4" s="99"/>
+      <c r="BG4" s="100"/>
+      <c r="BH4" s="100"/>
+      <c r="BI4" s="100"/>
+      <c r="BJ4" s="100"/>
+      <c r="BK4" s="100"/>
+      <c r="BL4" s="101"/>
     </row>
     <row r="5" spans="1:64" ht="15" customHeight="1">
       <c r="A5" s="9" t="s">
@@ -7096,7 +7096,7 @@
         <v>45775</v>
       </c>
       <c r="F58" s="93">
-        <v>45788</v>
+        <v>45784</v>
       </c>
       <c r="G58" s="38"/>
       <c r="H58" s="38"/>
@@ -7172,7 +7172,7 @@
         <v>45775</v>
       </c>
       <c r="F59" s="93">
-        <v>45788</v>
+        <v>45784</v>
       </c>
       <c r="G59" s="38"/>
       <c r="H59" s="38"/>
@@ -7406,12 +7406,12 @@
         <v>45775</v>
       </c>
       <c r="F62" s="93">
-        <v>45788</v>
+        <v>45784</v>
       </c>
       <c r="G62" s="38"/>
       <c r="H62" s="38">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I62" s="5"/>
       <c r="J62" s="5"/>
@@ -7485,7 +7485,7 @@
         <v>45775</v>
       </c>
       <c r="F63" s="93">
-        <v>45788</v>
+        <v>45784</v>
       </c>
       <c r="G63" s="38"/>
       <c r="H63" s="38"/>
@@ -7710,10 +7710,10 @@
         <v>1</v>
       </c>
       <c r="E66" s="94">
+        <v>45775</v>
+      </c>
+      <c r="F66" s="94">
         <v>45784</v>
-      </c>
-      <c r="F66" s="94">
-        <v>45788</v>
       </c>
       <c r="G66" s="38"/>
       <c r="H66" s="38"/>
@@ -7862,10 +7862,10 @@
         <v>1</v>
       </c>
       <c r="E68" s="94">
-        <v>45785</v>
+        <v>45784</v>
       </c>
       <c r="F68" s="94">
-        <v>45788</v>
+        <v>45784</v>
       </c>
       <c r="G68" s="38"/>
       <c r="H68" s="38"/>
@@ -8172,15 +8172,15 @@
         <v>1</v>
       </c>
       <c r="E72" s="94">
-        <v>45785</v>
+        <v>45784</v>
       </c>
       <c r="F72" s="94">
-        <v>45788</v>
+        <v>45784</v>
       </c>
       <c r="G72" s="38"/>
       <c r="H72" s="38">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
@@ -8409,7 +8409,7 @@
         <v>45774</v>
       </c>
       <c r="F75" s="94">
-        <v>45784</v>
+        <v>45775</v>
       </c>
       <c r="G75" s="38"/>
       <c r="H75" s="38"/>
@@ -8482,10 +8482,10 @@
         <v>1</v>
       </c>
       <c r="E76" s="94">
-        <v>45785</v>
+        <v>45775</v>
       </c>
       <c r="F76" s="94">
-        <v>45788</v>
+        <v>45784</v>
       </c>
       <c r="G76" s="38"/>
       <c r="H76" s="38"/>
@@ -8631,15 +8631,15 @@
         <v>1</v>
       </c>
       <c r="E78" s="95">
-        <v>45784</v>
+        <v>45789</v>
       </c>
       <c r="F78" s="95">
-        <v>45784</v>
+        <v>45788</v>
       </c>
       <c r="G78" s="38"/>
       <c r="H78" s="38">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
@@ -8710,7 +8710,7 @@
         <v>1</v>
       </c>
       <c r="E79" s="95">
-        <v>45784</v>
+        <v>45789</v>
       </c>
       <c r="F79" s="95">
         <v>45784</v>
@@ -8786,7 +8786,7 @@
         <v>1</v>
       </c>
       <c r="E80" s="95">
-        <v>45784</v>
+        <v>45789</v>
       </c>
       <c r="F80" s="95">
         <v>45784</v>
@@ -8862,7 +8862,7 @@
         <v>0</v>
       </c>
       <c r="E81" s="95">
-        <v>45784</v>
+        <v>45789</v>
       </c>
       <c r="F81" s="95">
         <v>45784</v>
@@ -8938,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="E82" s="95">
-        <v>45785</v>
+        <v>45789</v>
       </c>
       <c r="F82" s="95">
         <v>45785</v>
@@ -9014,7 +9014,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="95">
-        <v>45786</v>
+        <v>45789</v>
       </c>
       <c r="F83" s="95">
         <v>45786</v>
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="E85" s="95">
-        <v>45790</v>
+        <v>45789</v>
       </c>
       <c r="F85" s="95">
         <v>45791</v>
@@ -9242,7 +9242,7 @@
         <v>0</v>
       </c>
       <c r="E86" s="95">
-        <v>45784</v>
+        <v>45789</v>
       </c>
       <c r="F86" s="95">
         <v>45784</v>
@@ -9318,7 +9318,7 @@
         <v>0</v>
       </c>
       <c r="E87" s="95">
-        <v>45785</v>
+        <v>45789</v>
       </c>
       <c r="F87" s="95">
         <v>45785</v>
@@ -9394,7 +9394,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="95">
-        <v>45786</v>
+        <v>45789</v>
       </c>
       <c r="F88" s="95">
         <v>45786</v>
@@ -9549,7 +9549,7 @@
         <v>0</v>
       </c>
       <c r="E90" s="95">
-        <v>45790</v>
+        <v>45789</v>
       </c>
       <c r="F90" s="95">
         <v>45791</v>
@@ -9557,7 +9557,7 @@
       <c r="G90" s="38"/>
       <c r="H90" s="38">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I90" s="5"/>
       <c r="J90" s="5"/>
@@ -9628,7 +9628,7 @@
         <v>0</v>
       </c>
       <c r="E91" s="95">
-        <v>45790</v>
+        <v>45789</v>
       </c>
       <c r="F91" s="95">
         <v>45790</v>
@@ -9636,7 +9636,7 @@
       <c r="G91" s="38"/>
       <c r="H91" s="38">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I91" s="5"/>
       <c r="J91" s="5"/>
@@ -9707,7 +9707,7 @@
         <v>0</v>
       </c>
       <c r="E92" s="95">
-        <v>45791</v>
+        <v>45789</v>
       </c>
       <c r="F92" s="95">
         <v>45791</v>
@@ -9715,7 +9715,7 @@
       <c r="G92" s="38"/>
       <c r="H92" s="38">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
@@ -9786,7 +9786,7 @@
         <v>0</v>
       </c>
       <c r="E93" s="95">
-        <v>45785</v>
+        <v>45789</v>
       </c>
       <c r="F93" s="95">
         <v>45786</v>
@@ -9862,7 +9862,7 @@
         <v>0</v>
       </c>
       <c r="E94" s="95">
-        <v>45785</v>
+        <v>45789</v>
       </c>
       <c r="F94" s="95">
         <v>45786</v>
@@ -9938,7 +9938,7 @@
         <v>0</v>
       </c>
       <c r="E95" s="95">
-        <v>45785</v>
+        <v>45789</v>
       </c>
       <c r="F95" s="95">
         <v>45789</v>
@@ -10166,7 +10166,7 @@
         <v>0</v>
       </c>
       <c r="E98" s="95">
-        <v>45784</v>
+        <v>45789</v>
       </c>
       <c r="F98" s="95">
         <v>45784</v>
@@ -10315,7 +10315,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="96">
-        <v>45792</v>
+        <v>45789</v>
       </c>
       <c r="F100" s="96">
         <v>45792</v>
@@ -10323,7 +10323,7 @@
       <c r="G100" s="38"/>
       <c r="H100" s="38">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I100" s="5"/>
       <c r="J100" s="5"/>
@@ -10394,7 +10394,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="96">
-        <v>45793</v>
+        <v>45789</v>
       </c>
       <c r="F101" s="96">
         <v>45793</v>
@@ -10470,7 +10470,7 @@
         <v>0</v>
       </c>
       <c r="E102" s="96">
-        <v>45792</v>
+        <v>45789</v>
       </c>
       <c r="F102" s="96">
         <v>45793</v>
@@ -10546,7 +10546,7 @@
         <v>0</v>
       </c>
       <c r="E103" s="96">
-        <v>45796</v>
+        <v>45789</v>
       </c>
       <c r="F103" s="96">
         <v>45798</v>
@@ -10622,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="E104" s="96">
-        <v>45792</v>
+        <v>45789</v>
       </c>
       <c r="F104" s="96">
         <v>45793</v>
@@ -10698,7 +10698,7 @@
         <v>0</v>
       </c>
       <c r="E105" s="96">
-        <v>45796</v>
+        <v>45789</v>
       </c>
       <c r="F105" s="96">
         <v>45798</v>
@@ -10774,7 +10774,7 @@
         <v>0</v>
       </c>
       <c r="E106" s="96">
-        <v>45796</v>
+        <v>45789</v>
       </c>
       <c r="F106" s="96">
         <v>45798</v>
@@ -10850,7 +10850,7 @@
         <v>0</v>
       </c>
       <c r="E107" s="96">
-        <v>45792</v>
+        <v>45789</v>
       </c>
       <c r="F107" s="96">
         <v>45793</v>
@@ -10926,7 +10926,7 @@
         <v>0</v>
       </c>
       <c r="E108" s="96">
-        <v>45796</v>
+        <v>45789</v>
       </c>
       <c r="F108" s="96">
         <v>45798</v>
@@ -11002,7 +11002,7 @@
         <v>0</v>
       </c>
       <c r="E109" s="96">
-        <v>45792</v>
+        <v>45789</v>
       </c>
       <c r="F109" s="96">
         <v>45793</v>
@@ -11078,7 +11078,7 @@
         <v>0</v>
       </c>
       <c r="E110" s="96">
-        <v>45796</v>
+        <v>45789</v>
       </c>
       <c r="F110" s="96">
         <v>45798</v>
@@ -11086,7 +11086,7 @@
       <c r="G110" s="38"/>
       <c r="H110" s="38">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I110" s="5"/>
       <c r="J110" s="5"/>
@@ -11308,17 +11308,17 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="11">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
   </mergeCells>
   <phoneticPr fontId="29"/>
   <conditionalFormatting sqref="D7:D112">
@@ -11495,6 +11495,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -11701,27 +11721,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B636D13B-D6CE-437F-B40B-151CC8DA2A1F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11738,23 +11757,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Javaシステム開発WBS.xlsx
+++ b/Javaシステム開発WBS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7A7D55-43BB-432F-B834-6B4F06247617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724734C1-0D34-4713-983F-80BD29B6A798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1857,12 +1857,6 @@
     <xf numFmtId="14" fontId="1" fillId="10" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1874,6 +1868,12 @@
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2560,106 +2560,106 @@
       <c r="B3" s="84" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="97" t="s">
+      <c r="C3" s="101" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="98"/>
-      <c r="E3" s="102">
+      <c r="D3" s="102"/>
+      <c r="E3" s="100">
         <v>45770</v>
       </c>
-      <c r="F3" s="102"/>
+      <c r="F3" s="100"/>
     </row>
     <row r="4" spans="1:64" ht="30" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="97" t="s">
+      <c r="C4" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="98"/>
+      <c r="D4" s="102"/>
       <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="I4" s="99">
+      <c r="I4" s="97">
         <f>I5</f>
         <v>45768</v>
       </c>
-      <c r="J4" s="100"/>
-      <c r="K4" s="100"/>
-      <c r="L4" s="100"/>
-      <c r="M4" s="100"/>
-      <c r="N4" s="100"/>
-      <c r="O4" s="101"/>
-      <c r="P4" s="99">
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="97">
         <f>P5</f>
         <v>45775</v>
       </c>
-      <c r="Q4" s="100"/>
-      <c r="R4" s="100"/>
-      <c r="S4" s="100"/>
-      <c r="T4" s="100"/>
-      <c r="U4" s="100"/>
-      <c r="V4" s="101"/>
-      <c r="W4" s="99">
+      <c r="Q4" s="98"/>
+      <c r="R4" s="98"/>
+      <c r="S4" s="98"/>
+      <c r="T4" s="98"/>
+      <c r="U4" s="98"/>
+      <c r="V4" s="99"/>
+      <c r="W4" s="97">
         <f>W5</f>
         <v>45782</v>
       </c>
-      <c r="X4" s="100"/>
-      <c r="Y4" s="100"/>
-      <c r="Z4" s="100"/>
-      <c r="AA4" s="100"/>
-      <c r="AB4" s="100"/>
-      <c r="AC4" s="101"/>
-      <c r="AD4" s="99">
+      <c r="X4" s="98"/>
+      <c r="Y4" s="98"/>
+      <c r="Z4" s="98"/>
+      <c r="AA4" s="98"/>
+      <c r="AB4" s="98"/>
+      <c r="AC4" s="99"/>
+      <c r="AD4" s="97">
         <f>AD5</f>
         <v>45789</v>
       </c>
-      <c r="AE4" s="100"/>
-      <c r="AF4" s="100"/>
-      <c r="AG4" s="100"/>
-      <c r="AH4" s="100"/>
-      <c r="AI4" s="100"/>
-      <c r="AJ4" s="101"/>
-      <c r="AK4" s="99">
+      <c r="AE4" s="98"/>
+      <c r="AF4" s="98"/>
+      <c r="AG4" s="98"/>
+      <c r="AH4" s="98"/>
+      <c r="AI4" s="98"/>
+      <c r="AJ4" s="99"/>
+      <c r="AK4" s="97">
         <f>AK5</f>
         <v>45796</v>
       </c>
-      <c r="AL4" s="100"/>
-      <c r="AM4" s="100"/>
-      <c r="AN4" s="100"/>
-      <c r="AO4" s="100"/>
-      <c r="AP4" s="100"/>
-      <c r="AQ4" s="101"/>
-      <c r="AR4" s="99">
+      <c r="AL4" s="98"/>
+      <c r="AM4" s="98"/>
+      <c r="AN4" s="98"/>
+      <c r="AO4" s="98"/>
+      <c r="AP4" s="98"/>
+      <c r="AQ4" s="99"/>
+      <c r="AR4" s="97">
         <f>AR5</f>
         <v>45803</v>
       </c>
-      <c r="AS4" s="100"/>
-      <c r="AT4" s="100"/>
-      <c r="AU4" s="100"/>
-      <c r="AV4" s="100"/>
-      <c r="AW4" s="100"/>
-      <c r="AX4" s="101"/>
-      <c r="AY4" s="99">
+      <c r="AS4" s="98"/>
+      <c r="AT4" s="98"/>
+      <c r="AU4" s="98"/>
+      <c r="AV4" s="98"/>
+      <c r="AW4" s="98"/>
+      <c r="AX4" s="99"/>
+      <c r="AY4" s="97">
         <f>AY5</f>
         <v>45810</v>
       </c>
-      <c r="AZ4" s="100"/>
-      <c r="BA4" s="100"/>
-      <c r="BB4" s="100"/>
-      <c r="BC4" s="100"/>
-      <c r="BD4" s="100"/>
-      <c r="BE4" s="101"/>
-      <c r="BF4" s="99">
+      <c r="AZ4" s="98"/>
+      <c r="BA4" s="98"/>
+      <c r="BB4" s="98"/>
+      <c r="BC4" s="98"/>
+      <c r="BD4" s="98"/>
+      <c r="BE4" s="99"/>
+      <c r="BF4" s="97">
         <f>BF5</f>
         <v>45817</v>
       </c>
-      <c r="BG4" s="100"/>
-      <c r="BH4" s="100"/>
-      <c r="BI4" s="100"/>
-      <c r="BJ4" s="100"/>
-      <c r="BK4" s="100"/>
-      <c r="BL4" s="101"/>
+      <c r="BG4" s="98"/>
+      <c r="BH4" s="98"/>
+      <c r="BI4" s="98"/>
+      <c r="BJ4" s="98"/>
+      <c r="BK4" s="98"/>
+      <c r="BL4" s="99"/>
     </row>
     <row r="5" spans="1:64" ht="15" customHeight="1">
       <c r="A5" s="9" t="s">
@@ -9783,7 +9783,7 @@
         <v>145</v>
       </c>
       <c r="D93" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" s="95">
         <v>45789</v>
@@ -9859,7 +9859,7 @@
         <v>145</v>
       </c>
       <c r="D94" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" s="95">
         <v>45789</v>
@@ -9935,7 +9935,7 @@
         <v>145</v>
       </c>
       <c r="D95" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" s="95">
         <v>45789</v>
@@ -10011,7 +10011,7 @@
         <v>145</v>
       </c>
       <c r="D96" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" s="95">
         <v>45789</v>
@@ -10087,7 +10087,7 @@
         <v>145</v>
       </c>
       <c r="D97" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" s="95">
         <v>45789</v>
@@ -11308,17 +11308,17 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="11">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
   </mergeCells>
   <phoneticPr fontId="29"/>
   <conditionalFormatting sqref="D7:D112">
@@ -11495,26 +11495,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -11721,10 +11701,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B636D13B-D6CE-437F-B40B-151CC8DA2A1F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11741,20 +11752,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B636D13B-D6CE-437F-B40B-151CC8DA2A1F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Javaシステム開発WBS.xlsx
+++ b/Javaシステム開発WBS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724734C1-0D34-4713-983F-80BD29B6A798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B747CE8A-D09D-4C75-ABFF-BABDAF1D66B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロジェクトのスケジュール" sheetId="11" r:id="rId1"/>
@@ -1857,6 +1857,12 @@
     <xf numFmtId="14" fontId="1" fillId="10" borderId="2" xfId="10" applyNumberFormat="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1868,12 +1874,6 @@
     </xf>
     <xf numFmtId="179" fontId="1" fillId="0" borderId="3" xfId="9">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2560,106 +2560,106 @@
       <c r="B3" s="84" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="101" t="s">
+      <c r="C3" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="102"/>
-      <c r="E3" s="100">
+      <c r="D3" s="98"/>
+      <c r="E3" s="102">
         <v>45770</v>
       </c>
-      <c r="F3" s="100"/>
+      <c r="F3" s="102"/>
     </row>
     <row r="4" spans="1:64" ht="30" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="101" t="s">
+      <c r="C4" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="102"/>
+      <c r="D4" s="98"/>
       <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="I4" s="97">
+      <c r="I4" s="99">
         <f>I5</f>
         <v>45768</v>
       </c>
-      <c r="J4" s="98"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="97">
+      <c r="J4" s="100"/>
+      <c r="K4" s="100"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="100"/>
+      <c r="N4" s="100"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="99">
         <f>P5</f>
         <v>45775</v>
       </c>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="98"/>
-      <c r="S4" s="98"/>
-      <c r="T4" s="98"/>
-      <c r="U4" s="98"/>
-      <c r="V4" s="99"/>
-      <c r="W4" s="97">
+      <c r="Q4" s="100"/>
+      <c r="R4" s="100"/>
+      <c r="S4" s="100"/>
+      <c r="T4" s="100"/>
+      <c r="U4" s="100"/>
+      <c r="V4" s="101"/>
+      <c r="W4" s="99">
         <f>W5</f>
         <v>45782</v>
       </c>
-      <c r="X4" s="98"/>
-      <c r="Y4" s="98"/>
-      <c r="Z4" s="98"/>
-      <c r="AA4" s="98"/>
-      <c r="AB4" s="98"/>
-      <c r="AC4" s="99"/>
-      <c r="AD4" s="97">
+      <c r="X4" s="100"/>
+      <c r="Y4" s="100"/>
+      <c r="Z4" s="100"/>
+      <c r="AA4" s="100"/>
+      <c r="AB4" s="100"/>
+      <c r="AC4" s="101"/>
+      <c r="AD4" s="99">
         <f>AD5</f>
         <v>45789</v>
       </c>
-      <c r="AE4" s="98"/>
-      <c r="AF4" s="98"/>
-      <c r="AG4" s="98"/>
-      <c r="AH4" s="98"/>
-      <c r="AI4" s="98"/>
-      <c r="AJ4" s="99"/>
-      <c r="AK4" s="97">
+      <c r="AE4" s="100"/>
+      <c r="AF4" s="100"/>
+      <c r="AG4" s="100"/>
+      <c r="AH4" s="100"/>
+      <c r="AI4" s="100"/>
+      <c r="AJ4" s="101"/>
+      <c r="AK4" s="99">
         <f>AK5</f>
         <v>45796</v>
       </c>
-      <c r="AL4" s="98"/>
-      <c r="AM4" s="98"/>
-      <c r="AN4" s="98"/>
-      <c r="AO4" s="98"/>
-      <c r="AP4" s="98"/>
-      <c r="AQ4" s="99"/>
-      <c r="AR4" s="97">
+      <c r="AL4" s="100"/>
+      <c r="AM4" s="100"/>
+      <c r="AN4" s="100"/>
+      <c r="AO4" s="100"/>
+      <c r="AP4" s="100"/>
+      <c r="AQ4" s="101"/>
+      <c r="AR4" s="99">
         <f>AR5</f>
         <v>45803</v>
       </c>
-      <c r="AS4" s="98"/>
-      <c r="AT4" s="98"/>
-      <c r="AU4" s="98"/>
-      <c r="AV4" s="98"/>
-      <c r="AW4" s="98"/>
-      <c r="AX4" s="99"/>
-      <c r="AY4" s="97">
+      <c r="AS4" s="100"/>
+      <c r="AT4" s="100"/>
+      <c r="AU4" s="100"/>
+      <c r="AV4" s="100"/>
+      <c r="AW4" s="100"/>
+      <c r="AX4" s="101"/>
+      <c r="AY4" s="99">
         <f>AY5</f>
         <v>45810</v>
       </c>
-      <c r="AZ4" s="98"/>
-      <c r="BA4" s="98"/>
-      <c r="BB4" s="98"/>
-      <c r="BC4" s="98"/>
-      <c r="BD4" s="98"/>
-      <c r="BE4" s="99"/>
-      <c r="BF4" s="97">
+      <c r="AZ4" s="100"/>
+      <c r="BA4" s="100"/>
+      <c r="BB4" s="100"/>
+      <c r="BC4" s="100"/>
+      <c r="BD4" s="100"/>
+      <c r="BE4" s="101"/>
+      <c r="BF4" s="99">
         <f>BF5</f>
         <v>45817</v>
       </c>
-      <c r="BG4" s="98"/>
-      <c r="BH4" s="98"/>
-      <c r="BI4" s="98"/>
-      <c r="BJ4" s="98"/>
-      <c r="BK4" s="98"/>
-      <c r="BL4" s="99"/>
+      <c r="BG4" s="100"/>
+      <c r="BH4" s="100"/>
+      <c r="BI4" s="100"/>
+      <c r="BJ4" s="100"/>
+      <c r="BK4" s="100"/>
+      <c r="BL4" s="101"/>
     </row>
     <row r="5" spans="1:64" ht="15" customHeight="1">
       <c r="A5" s="9" t="s">
@@ -9086,8 +9086,8 @@
       <c r="C84" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="D84" s="45">
-        <v>0</v>
+      <c r="D84" s="42">
+        <v>1</v>
       </c>
       <c r="E84" s="95">
         <v>45789</v>
@@ -9162,8 +9162,8 @@
       <c r="C85" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="D85" s="45">
-        <v>0</v>
+      <c r="D85" s="42">
+        <v>1</v>
       </c>
       <c r="E85" s="95">
         <v>45789</v>
@@ -9238,8 +9238,8 @@
       <c r="C86" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="D86" s="45">
-        <v>0</v>
+      <c r="D86" s="42">
+        <v>1</v>
       </c>
       <c r="E86" s="95">
         <v>45789</v>
@@ -9314,8 +9314,8 @@
       <c r="C87" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="D87" s="45">
-        <v>0</v>
+      <c r="D87" s="42">
+        <v>1</v>
       </c>
       <c r="E87" s="95">
         <v>45789</v>
@@ -9390,8 +9390,8 @@
       <c r="C88" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="D88" s="45">
-        <v>0</v>
+      <c r="D88" s="42">
+        <v>1</v>
       </c>
       <c r="E88" s="95">
         <v>45789</v>
@@ -9466,8 +9466,8 @@
       <c r="C89" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="D89" s="45">
-        <v>0</v>
+      <c r="D89" s="42">
+        <v>1</v>
       </c>
       <c r="E89" s="95">
         <v>45789</v>
@@ -11308,17 +11308,17 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="11">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BF4:BL4"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
   </mergeCells>
   <phoneticPr fontId="29"/>
   <conditionalFormatting sqref="D7:D112">
@@ -11495,6 +11495,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -11701,27 +11721,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B636D13B-D6CE-437F-B40B-151CC8DA2A1F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11738,23 +11757,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>